--- a/Lưu lượng Sản lượng Srepok3 1977_2026.xlsx
+++ b/Lưu lượng Sản lượng Srepok3 1977_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VScode\Du lieu truy van chuoi dong dang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541D42E6-F8A4-42F4-8DBF-0C2FA081172B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A2A15D-8446-43A9-87DF-9122B97B2359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{659022F3-9776-4CE8-9441-3FE9697E9AF5}"/>
   </bookViews>
@@ -235,6 +235,11 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="3">
+          <cell r="C3">
+            <v>20.360220000000009</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>45.438943999999999</v>
@@ -275,6 +280,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>17.593199999999996</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>59.674320000000016</v>
@@ -315,6 +325,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="2">
+        <row r="3">
+          <cell r="C3">
+            <v>14.871199999999954</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>29.3931</v>
@@ -355,6 +370,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="3">
+        <row r="3">
+          <cell r="C3">
+            <v>25.792999999999999</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>42.385599999999975</v>
@@ -395,6 +415,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="4">
+        <row r="3">
+          <cell r="C3">
+            <v>19.655700000000071</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>42.550300000000043</v>
@@ -435,6 +460,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="5">
+        <row r="3">
+          <cell r="C3">
+            <v>20.582000000000001</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>40.519900000000142</v>
@@ -475,6 +505,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="6">
+        <row r="3">
+          <cell r="C3">
+            <v>31.364885999999821</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>108.60762999999989</v>
@@ -515,6 +550,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="7">
+        <row r="3">
+          <cell r="C3">
+            <v>29.766293000000065</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>84.546728999999814</v>
@@ -555,6 +595,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="8">
+        <row r="3">
+          <cell r="C3">
+            <v>22.552581999999937</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>91.580513000000266</v>
@@ -595,6 +640,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="9">
+        <row r="3">
+          <cell r="C3">
+            <v>24.566246999999972</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>41.345302000000139</v>
@@ -635,6 +685,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="10">
+        <row r="3">
+          <cell r="C3">
+            <v>29.164321999999927</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>84.770697999999385</v>
@@ -675,6 +730,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="11">
+        <row r="3">
+          <cell r="C3">
+            <v>33.846495199999993</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>88.530286399999994</v>
@@ -715,6 +775,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="12">
+        <row r="3">
+          <cell r="C3">
+            <v>26.196023199999999</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>77.740175000000008</v>
@@ -755,6 +820,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="13">
+        <row r="3">
+          <cell r="C3">
+            <v>27.937671999999999</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
             <v>57.337101000000004</v>
@@ -1121,9 +1191,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E41275D1-C989-428D-A27E-CB9D896EA195}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{E41275D1-C989-428D-A27E-CB9D896EA195}">
   <dimension ref="B1:AF61"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" ns3:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="8.875" bestFit="1" customWidth="1"/>
@@ -1131,7 +1201,7 @@
     <col min="15" max="15" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:32" ht="15" ns3:dyDescent="0.25">
       <c r="C1" s="16" t="s">
         <v>6</v>
       </c>
@@ -1162,7 +1232,7 @@
       <c r="AA1" s="14"/>
       <c r="AB1" s="14"/>
     </row>
-    <row r="2" spans="2:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:32" ht="15" ns3:dyDescent="0.25">
       <c r="C2" s="9">
         <v>1</v>
       </c>
@@ -1248,7 +1318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:32" ns3:dyDescent="0.2">
       <c r="B3">
         <v>1977</v>
       </c>
@@ -1350,7 +1420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:32" ns3:dyDescent="0.2">
       <c r="B4">
         <v>1978</v>
       </c>
@@ -1443,7 +1513,7 @@
         <v>167.2</v>
       </c>
     </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:32" ns3:dyDescent="0.2">
       <c r="B5">
         <v>1979</v>
       </c>
@@ -1536,7 +1606,7 @@
         <v>240.4</v>
       </c>
     </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:32" ns3:dyDescent="0.2">
       <c r="B6">
         <v>1980</v>
       </c>
@@ -1629,7 +1699,7 @@
         <v>240.1</v>
       </c>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:32" ns3:dyDescent="0.2">
       <c r="B7">
         <v>1981</v>
       </c>
@@ -1722,7 +1792,7 @@
         <v>441.4</v>
       </c>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:32" ns3:dyDescent="0.2">
       <c r="B8">
         <v>1982</v>
       </c>
@@ -1815,7 +1885,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:32" ns3:dyDescent="0.2">
       <c r="B9">
         <v>1983</v>
       </c>
@@ -1908,7 +1978,7 @@
         <v>147.19999999999999</v>
       </c>
     </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:32" ns3:dyDescent="0.2">
       <c r="B10">
         <v>1984</v>
       </c>
@@ -2001,7 +2071,7 @@
         <v>230.4</v>
       </c>
     </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:32" ns3:dyDescent="0.2">
       <c r="B11">
         <v>1985</v>
       </c>
@@ -2094,7 +2164,7 @@
         <v>240.2</v>
       </c>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:32" ns3:dyDescent="0.2">
       <c r="B12">
         <v>1986</v>
       </c>
@@ -2187,7 +2257,7 @@
         <v>313.10000000000002</v>
       </c>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:32" ns3:dyDescent="0.2">
       <c r="B13">
         <v>1987</v>
       </c>
@@ -2280,7 +2350,7 @@
         <v>196.1</v>
       </c>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:32" ns3:dyDescent="0.2">
       <c r="B14">
         <v>1988</v>
       </c>
@@ -2373,7 +2443,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:32" ns3:dyDescent="0.2">
       <c r="B15">
         <v>1989</v>
       </c>
@@ -2466,7 +2536,7 @@
         <v>139.5</v>
       </c>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:32" ns3:dyDescent="0.2">
       <c r="B16">
         <v>1990</v>
       </c>
@@ -2559,7 +2629,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:28" ns3:dyDescent="0.2">
       <c r="B17">
         <v>1991</v>
       </c>
@@ -2652,7 +2722,7 @@
         <v>96.7</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:28" ns3:dyDescent="0.2">
       <c r="B18">
         <v>1992</v>
       </c>
@@ -2745,7 +2815,7 @@
         <v>184.6</v>
       </c>
     </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:28" ns3:dyDescent="0.2">
       <c r="B19">
         <v>1993</v>
       </c>
@@ -2838,7 +2908,7 @@
         <v>590.4</v>
       </c>
     </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:28" ns3:dyDescent="0.2">
       <c r="B20">
         <v>1994</v>
       </c>
@@ -2931,7 +3001,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:28" ns3:dyDescent="0.2">
       <c r="B21">
         <v>1995</v>
       </c>
@@ -3024,7 +3094,7 @@
         <v>222.3</v>
       </c>
     </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:28" ns3:dyDescent="0.2">
       <c r="B22">
         <v>1996</v>
       </c>
@@ -3117,7 +3187,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:28" ns3:dyDescent="0.2">
       <c r="B23">
         <v>1997</v>
       </c>
@@ -3210,7 +3280,7 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:28" ns3:dyDescent="0.2">
       <c r="B24">
         <v>1998</v>
       </c>
@@ -3303,7 +3373,7 @@
         <v>867.5</v>
       </c>
     </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:28" ns3:dyDescent="0.2">
       <c r="B25">
         <v>1999</v>
       </c>
@@ -3396,7 +3466,7 @@
         <v>662.8</v>
       </c>
     </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:28" ns3:dyDescent="0.2">
       <c r="B26">
         <v>2000</v>
       </c>
@@ -3489,7 +3559,7 @@
         <v>551.5</v>
       </c>
     </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:28" ns3:dyDescent="0.2">
       <c r="B27">
         <v>2001</v>
       </c>
@@ -3582,7 +3652,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:28" ns3:dyDescent="0.2">
       <c r="B28">
         <v>2002</v>
       </c>
@@ -3675,7 +3745,7 @@
         <v>180.5</v>
       </c>
     </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:28" ns3:dyDescent="0.2">
       <c r="B29">
         <v>2003</v>
       </c>
@@ -3768,7 +3838,7 @@
         <v>161.71377325659216</v>
       </c>
     </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:28" ns3:dyDescent="0.2">
       <c r="B30">
         <v>2004</v>
       </c>
@@ -3861,7 +3931,7 @@
         <v>78.943581849819296</v>
       </c>
     </row>
-    <row r="31" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:28" ns3:dyDescent="0.2">
       <c r="B31">
         <v>2005</v>
       </c>
@@ -3954,7 +4024,7 @@
         <v>661.06596718383753</v>
       </c>
     </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:28" ns3:dyDescent="0.2">
       <c r="B32">
         <v>2006</v>
       </c>
@@ -4047,7 +4117,7 @@
         <v>141.33263284700843</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" ns3:dyDescent="0.2">
       <c r="B33">
         <v>2007</v>
       </c>
@@ -4140,7 +4210,7 @@
         <v>322.4689064382278</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" ns3:dyDescent="0.2">
       <c r="B34">
         <v>2008</v>
       </c>
@@ -4233,7 +4303,7 @@
         <v>422.01270244947131</v>
       </c>
     </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:28" ns3:dyDescent="0.2">
       <c r="B35">
         <v>2009</v>
       </c>
@@ -4326,7 +4396,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:28" ns3:dyDescent="0.2">
       <c r="B36">
         <v>2010</v>
       </c>
@@ -4419,7 +4489,7 @@
         <v>311.84394761264713</v>
       </c>
     </row>
-    <row r="37" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B37" s="9">
         <v>2011</v>
       </c>
@@ -4512,7 +4582,7 @@
         <v>278.49357078853046</v>
       </c>
     </row>
-    <row r="38" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B38" s="9">
         <v>2012</v>
       </c>
@@ -4605,7 +4675,7 @@
         <v>120.805667562724</v>
       </c>
     </row>
-    <row r="39" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B39" s="9">
         <v>2013</v>
       </c>
@@ -4698,7 +4768,7 @@
         <v>175.15001493428915</v>
       </c>
     </row>
-    <row r="40" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B40" s="9">
         <v>2014</v>
       </c>
@@ -4791,7 +4861,7 @@
         <v>120.2848342293907</v>
       </c>
     </row>
-    <row r="41" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B41" s="9">
         <v>2015</v>
       </c>
@@ -4884,7 +4954,7 @@
         <v>97.740852747909216</v>
       </c>
     </row>
-    <row r="42" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B42" s="9">
         <v>2016</v>
       </c>
@@ -4977,7 +5047,7 @@
         <v>502.26662335722835</v>
       </c>
     </row>
-    <row r="43" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B43" s="9">
         <v>2017</v>
       </c>
@@ -5070,7 +5140,7 @@
         <v>476.69317502986866</v>
       </c>
     </row>
-    <row r="44" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B44" s="9">
         <v>2018</v>
       </c>
@@ -5163,7 +5233,7 @@
         <v>203.04579779359258</v>
       </c>
     </row>
-    <row r="45" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B45" s="9">
         <v>2019</v>
       </c>
@@ -5256,7 +5326,7 @@
         <v>157.37190113500591</v>
       </c>
     </row>
-    <row r="46" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B46" s="9">
         <v>2020</v>
       </c>
@@ -5349,7 +5419,7 @@
         <v>548.84274193548401</v>
       </c>
     </row>
-    <row r="47" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B47" s="9">
         <v>2021</v>
       </c>
@@ -5442,7 +5512,7 @@
         <v>493.87096774193554</v>
       </c>
     </row>
-    <row r="48" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B48" s="9">
         <v>2022</v>
       </c>
@@ -5535,7 +5605,7 @@
         <v>281.70430107526886</v>
       </c>
     </row>
-    <row r="49" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B49" s="9">
         <v>2023</v>
       </c>
@@ -5628,7 +5698,7 @@
         <v>239.06182580645162</v>
       </c>
     </row>
-    <row r="50" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B50" s="9">
         <v>2024</v>
       </c>
@@ -5721,7 +5791,7 @@
         <v>248.40457096774193</v>
       </c>
     </row>
-    <row r="51" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B51" s="8">
         <v>2025</v>
       </c>
@@ -5802,7 +5872,7 @@
         <v>507.7110193548387</v>
       </c>
     </row>
-    <row r="52" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B52" s="9">
         <v>2026</v>
       </c>
@@ -5833,7 +5903,9 @@
       <c r="K52" s="1">
         <v>128.93</v>
       </c>
-      <c r="L52" s="1"/>
+      <c r="L52" s="1" t="n">
+        <v>66.8944957</v>
+      </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="7"/>
@@ -5864,8 +5936,11 @@
       <c r="Y52" s="1">
         <v>344.33</v>
       </c>
+      <c r="Z52" s="1" t="n">
+        <v>406.88</v>
+      </c>
     </row>
-    <row r="53" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B53" s="8"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -5881,7 +5956,7 @@
       <c r="N53" s="1"/>
       <c r="O53" s="7"/>
     </row>
-    <row r="54" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B54" s="8"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -5897,7 +5972,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="7"/>
     </row>
-    <row r="55" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B55" s="6"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -5914,7 +5989,7 @@
       <c r="O55" s="3"/>
       <c r="P55" s="2"/>
     </row>
-    <row r="56" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B56" s="6"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -5930,7 +6005,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="3"/>
     </row>
-    <row r="58" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B58" s="15"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -5947,7 +6022,7 @@
       <c r="O58" s="3"/>
       <c r="P58" s="2"/>
     </row>
-    <row r="59" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B59" s="15"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -5963,7 +6038,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="3"/>
     </row>
-    <row r="60" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -5979,7 +6054,7 @@
       <c r="O60" s="3"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:28" ns3:dyDescent="0.2">
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
